--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96975547</v>
+        <v>96975339</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547943.6414796507</v>
+        <v>547891</v>
       </c>
       <c r="R2" t="n">
-        <v>6314001.250514075</v>
+        <v>6314109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,50 +784,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96975363</v>
+        <v>96975469</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547863.5867879828</v>
+        <v>547782</v>
       </c>
       <c r="R3" t="n">
-        <v>6314122.439063156</v>
+        <v>6314090</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +856,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,37 +886,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96975392</v>
+        <v>73598049</v>
       </c>
       <c r="B4" t="n">
-        <v>88006</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6268</v>
+        <v>3739</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,21 +921,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547842.4186666433</v>
+        <v>547848</v>
       </c>
       <c r="R4" t="n">
-        <v>6314110.747461411</v>
+        <v>6314206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,22 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,50 +987,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96975469</v>
+        <v>96975433</v>
       </c>
       <c r="B5" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547782.0212980536</v>
+        <v>547841</v>
       </c>
       <c r="R5" t="n">
-        <v>6314090.427568894</v>
+        <v>6314083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,19 +1073,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,16 +1106,11 @@
         <v>96975342</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1215,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547890.5115749751</v>
+        <v>547891</v>
       </c>
       <c r="R6" t="n">
-        <v>6314108.575846538</v>
+        <v>6314109</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,19 +1182,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,16 +1215,11 @@
         <v>96975347</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1339,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547863.5867879828</v>
+        <v>547864</v>
       </c>
       <c r="R7" t="n">
-        <v>6314122.439063156</v>
+        <v>6314122</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,19 +1291,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,16 +1324,11 @@
         <v>96975442</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1463,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547825.8775128489</v>
+        <v>547826</v>
       </c>
       <c r="R8" t="n">
-        <v>6314171.611597598</v>
+        <v>6314172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,19 +1400,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,15 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96975433</v>
+        <v>96975485</v>
       </c>
       <c r="B9" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,31 +1441,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1587,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547841.1002854933</v>
+        <v>547889</v>
       </c>
       <c r="R9" t="n">
-        <v>6314082.930348176</v>
+        <v>6314091</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1620,19 +1509,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,51 +1539,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96975395</v>
+        <v>96975547</v>
       </c>
       <c r="B10" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547842.4186666433</v>
+        <v>547944</v>
       </c>
       <c r="R10" t="n">
-        <v>6314110.747461411</v>
+        <v>6314001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1745,19 +1618,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,15 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96975549</v>
+        <v>96975581</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1836,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547943.6414796507</v>
+        <v>547919</v>
       </c>
       <c r="R11" t="n">
-        <v>6314001.250514075</v>
+        <v>6313986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1869,19 +1727,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1909,19 +1757,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96975366</v>
+        <v>73598064</v>
       </c>
       <c r="B12" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1942,28 +1785,19 @@
           <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547863.5867879828</v>
+        <v>547847</v>
       </c>
       <c r="R12" t="n">
-        <v>6314122.439063156</v>
+        <v>6314207</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,22 +1824,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,58 +1850,52 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96975488</v>
+        <v>96975366</v>
       </c>
       <c r="B13" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>5741</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2085,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547888.5217111828</v>
+        <v>547864</v>
       </c>
       <c r="R13" t="n">
-        <v>6314091.653705124</v>
+        <v>6314122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2118,19 +1936,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,47 +1966,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96975581</v>
+        <v>96975609</v>
       </c>
       <c r="B14" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2209,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547919.2399415515</v>
+        <v>547869</v>
       </c>
       <c r="R14" t="n">
-        <v>6313985.704831081</v>
+        <v>6314035</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2242,19 +2045,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,37 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96975570</v>
+        <v>96975640</v>
       </c>
       <c r="B15" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2322,11 +2110,10 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2334,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547919.2399415515</v>
+        <v>547998</v>
       </c>
       <c r="R15" t="n">
-        <v>6313985.704831081</v>
+        <v>6313991</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2367,19 +2154,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,12 +2187,7 @@
         <v>96975356</v>
       </c>
       <c r="B16" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2458,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547863.5867879828</v>
+        <v>547864</v>
       </c>
       <c r="R16" t="n">
-        <v>6314122.439063156</v>
+        <v>6314122</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,19 +2263,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,15 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96975428</v>
+        <v>96975392</v>
       </c>
       <c r="B17" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,35 +2304,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>6268</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2583,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547841.1002854933</v>
+        <v>547842</v>
       </c>
       <c r="R17" t="n">
-        <v>6314082.930348176</v>
+        <v>6314111</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2616,19 +2372,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,61 +2402,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96975485</v>
+        <v>73597769</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547888.5217111828</v>
+        <v>547907</v>
       </c>
       <c r="R18" t="n">
-        <v>6314091.653705124</v>
+        <v>6314156</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2737,22 +2479,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2773,68 +2505,64 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96975339</v>
+        <v>73598100</v>
       </c>
       <c r="B19" t="n">
-        <v>89608</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547890.5115749751</v>
+        <v>547922</v>
       </c>
       <c r="R19" t="n">
-        <v>6314108.575846538</v>
+        <v>6314110</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2861,22 +2589,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2897,57 +2615,53 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96975403</v>
+        <v>96975142</v>
       </c>
       <c r="B20" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2955,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547842.4186666433</v>
+        <v>547964</v>
       </c>
       <c r="R20" t="n">
-        <v>6314110.747461411</v>
+        <v>6314052</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2988,19 +2702,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,15 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96975560</v>
+        <v>96975333</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3063,7 +2762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3080,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547923.8788470152</v>
+        <v>547911</v>
       </c>
       <c r="R21" t="n">
-        <v>6314009.744896937</v>
+        <v>6314152</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3113,19 +2812,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3153,15 +2842,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96975577</v>
+        <v>96975353</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3188,7 +2872,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3205,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547919.2399415515</v>
+        <v>547864</v>
       </c>
       <c r="R22" t="n">
-        <v>6313985.704831081</v>
+        <v>6314122</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3238,19 +2922,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3281,12 +2955,7 @@
         <v>96975491</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,10 +2999,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547888.5217111828</v>
+        <v>547889</v>
       </c>
       <c r="R23" t="n">
-        <v>6314091.653705124</v>
+        <v>6314091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3363,19 +3032,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,15 +3062,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96975353</v>
+        <v>96975543</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3438,7 +3092,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3455,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547863.5867879828</v>
+        <v>547947</v>
       </c>
       <c r="R24" t="n">
-        <v>6314122.439063156</v>
+        <v>6314035</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3488,19 +3142,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3528,15 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96975543</v>
+        <v>96975560</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3563,7 +3202,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3580,10 +3219,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547947.6334205924</v>
+        <v>547923</v>
       </c>
       <c r="R25" t="n">
-        <v>6314034.005377769</v>
+        <v>6314010</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3613,19 +3252,9 @@
           <t>2021-09-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3650,6 +3279,776 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>96975577</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>547919</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6313986</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>96975329</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>547911</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6314152</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>96975395</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>547842</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6314111</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>96975428</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>547841</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6314083</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>96975488</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>547889</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6314091</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>96975570</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>547919</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6313986</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>96975605</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>547869</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6314035</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96975342</v>
+        <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93197</v>
+        <v>93391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,45 +1826,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Fröseke, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547891</v>
+        <v>547885</v>
       </c>
       <c r="R12" t="n">
-        <v>6314109</v>
+        <v>6314189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,24 +1912,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Joakim Andersson Hemberg, karin folkesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975342</t>
+          <t>https://artportalen.se/Sighting/136495630</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96975347</v>
+        <v>96975342</v>
       </c>
       <c r="B13" t="n">
         <v>93197</v>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547864</v>
+        <v>547891</v>
       </c>
       <c r="R13" t="n">
-        <v>6314122</v>
+        <v>6314109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,13 +2037,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975347</t>
+          <t>https://artportalen.se/Sighting/96975342</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96975442</v>
+        <v>96975347</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547826</v>
+        <v>547864</v>
       </c>
       <c r="R14" t="n">
-        <v>6314172</v>
+        <v>6314122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,13 +2151,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975442</t>
+          <t>https://artportalen.se/Sighting/96975347</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96975485</v>
+        <v>96975442</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547889</v>
+        <v>547826</v>
       </c>
       <c r="R15" t="n">
-        <v>6314091</v>
+        <v>6314172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,16 +2265,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975485</t>
+          <t>https://artportalen.se/Sighting/96975442</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>73598064</v>
+        <v>96975485</v>
       </c>
       <c r="B16" t="n">
-        <v>91409</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,36 +2282,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5741</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547847</v>
+        <v>547889</v>
       </c>
       <c r="R16" t="n">
-        <v>6314207</v>
+        <v>6314091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,12 +2347,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,22 +2373,22 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73598064</t>
+          <t>https://artportalen.se/Sighting/96975485</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96975366</v>
+        <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>91409</v>
+        <v>93399</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,45 +2396,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5741</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Fröseke, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
         <v>547864</v>
       </c>
       <c r="R17" t="n">
-        <v>6314122</v>
+        <v>6314132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,12 +2461,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,24 +2482,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Joakim Andersson Hemberg, karin folkesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975366</t>
+          <t>https://artportalen.se/Sighting/136495655</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96975609</v>
+        <v>73598064</v>
       </c>
       <c r="B18" t="n">
         <v>91409</v>
@@ -2518,28 +2527,19 @@
           <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547869</v>
+        <v>547847</v>
       </c>
       <c r="R18" t="n">
-        <v>6314035</v>
+        <v>6314207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,44 +2592,44 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975609</t>
+          <t>https://artportalen.se/Sighting/73598064</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96975356</v>
+        <v>96975366</v>
       </c>
       <c r="B19" t="n">
-        <v>92567</v>
+        <v>91409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>5741</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2712,48 +2712,48 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975356</t>
+          <t>https://artportalen.se/Sighting/96975366</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96975392</v>
+        <v>96975609</v>
       </c>
       <c r="B20" t="n">
-        <v>90681</v>
+        <v>91409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6268</v>
+        <v>5741</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547842</v>
+        <v>547869</v>
       </c>
       <c r="R20" t="n">
-        <v>6314111</v>
+        <v>6314035</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,63 +2826,62 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975392</t>
+          <t>https://artportalen.se/Sighting/96975609</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>73597769</v>
+        <v>96975356</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>92567</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547907</v>
+        <v>547864</v>
       </c>
       <c r="R21" t="n">
-        <v>6314156</v>
+        <v>6314122</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,12 +2908,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,69 +2934,68 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73597769</t>
+          <t>https://artportalen.se/Sighting/96975356</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>73598100</v>
+        <v>96975392</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>90681</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6268</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547922</v>
+        <v>547842</v>
       </c>
       <c r="R22" t="n">
-        <v>6314110</v>
+        <v>6314111</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,12 +3022,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,19 +3048,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73598100</t>
+          <t>https://artportalen.se/Sighting/96975392</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96975142</v>
+        <v>73597769</v>
       </c>
       <c r="B23" t="n">
         <v>99118</v>
@@ -3092,7 +3090,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3105,14 +3103,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547964</v>
+        <v>547907</v>
       </c>
       <c r="R23" t="n">
-        <v>6314052</v>
+        <v>6314156</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,12 +3137,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3165,19 +3163,19 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975142</t>
+          <t>https://artportalen.se/Sighting/73597769</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96975333</v>
+        <v>73598100</v>
       </c>
       <c r="B24" t="n">
         <v>99118</v>
@@ -3207,7 +3205,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3220,14 +3218,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+          <t>Kalkbarrskog 500 m SO Bölnegård, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547911</v>
+        <v>547922</v>
       </c>
       <c r="R24" t="n">
-        <v>6314152</v>
+        <v>6314110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,12 +3252,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2018-09-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,19 +3278,19 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975333</t>
+          <t>https://artportalen.se/Sighting/73598100</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96975353</v>
+        <v>96975142</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3322,7 +3320,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3339,10 +3337,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547864</v>
+        <v>547964</v>
       </c>
       <c r="R25" t="n">
-        <v>6314122</v>
+        <v>6314052</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,13 +3399,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975353</t>
+          <t>https://artportalen.se/Sighting/96975142</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96975491</v>
+        <v>96975333</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3437,7 +3435,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3454,10 +3452,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547889</v>
+        <v>547911</v>
       </c>
       <c r="R26" t="n">
-        <v>6314091</v>
+        <v>6314152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,13 +3514,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975491</t>
+          <t>https://artportalen.se/Sighting/96975333</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96975543</v>
+        <v>96975353</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3552,7 +3550,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3569,10 +3567,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547947</v>
+        <v>547864</v>
       </c>
       <c r="R27" t="n">
-        <v>6314035</v>
+        <v>6314122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3631,43 +3629,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975543</t>
+          <t>https://artportalen.se/Sighting/96975353</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96975329</v>
+        <v>96975491</v>
       </c>
       <c r="B28" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3684,10 +3682,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547911</v>
+        <v>547889</v>
       </c>
       <c r="R28" t="n">
-        <v>6314152</v>
+        <v>6314091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3746,43 +3744,43 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975329</t>
+          <t>https://artportalen.se/Sighting/96975491</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96975395</v>
+        <v>96975543</v>
       </c>
       <c r="B29" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3799,10 +3797,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547842</v>
+        <v>547947</v>
       </c>
       <c r="R29" t="n">
-        <v>6314111</v>
+        <v>6314035</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3861,13 +3859,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975395</t>
+          <t>https://artportalen.se/Sighting/96975543</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96975428</v>
+        <v>96975329</v>
       </c>
       <c r="B30" t="n">
         <v>106244</v>
@@ -3897,7 +3895,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3914,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547841</v>
+        <v>547911</v>
       </c>
       <c r="R30" t="n">
-        <v>6314083</v>
+        <v>6314152</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3976,13 +3974,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975428</t>
+          <t>https://artportalen.se/Sighting/96975329</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96975488</v>
+        <v>96975395</v>
       </c>
       <c r="B31" t="n">
         <v>106244</v>
@@ -4012,7 +4010,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4029,10 +4027,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547889</v>
+        <v>547842</v>
       </c>
       <c r="R31" t="n">
-        <v>6314091</v>
+        <v>6314111</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,13 +4089,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96975488</t>
+          <t>https://artportalen.se/Sighting/96975395</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96975605</v>
+        <v>96975428</v>
       </c>
       <c r="B32" t="n">
         <v>106244</v>
@@ -4127,7 +4125,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4144,10 +4142,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547869</v>
+        <v>547841</v>
       </c>
       <c r="R32" t="n">
-        <v>6314035</v>
+        <v>6314083</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4205,6 +4203,236 @@
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96975428</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>96975488</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>547889</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6314091</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96975488</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>96975605</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 500m SO Bölnegård, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>547869</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6314035</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96975605</t>
         </is>
@@ -4243,6 +4471,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26442-2026 artfynd.xlsx
+++ b/artfynd/A 26442-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136495630</v>
       </c>
       <c r="B12" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>136495655</v>
       </c>
       <c r="B17" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
